--- a/proposals/Barefoot_5Year_Business_Case.xlsx
+++ b/proposals/Barefoot_5Year_Business_Case.xlsx
@@ -1863,14 +1863,14 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Managed Service Retainer (mid-tier of R3,500-R5,500 range)</t>
+          <t>Managed Service Retainer (remote monitoring, maintenance, support)</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>4500</v>
+        <v>1500</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>5175</v>
+        <v>1725</v>
       </c>
       <c r="D23" s="6" t="n"/>
     </row>
@@ -2498,12 +2498,12 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>R4,500/month excl. VAT</t>
+          <t>R1,500/month excl. VAT</t>
         </is>
       </c>
       <c r="C8" s="26" t="inlineStr">
         <is>
-          <t>Mid-point of CTTX's R3,500-R5,500/month range for a system this complex (mast, solar/battery, 30 radios).</t>
+          <t>Set by Gerhard (26 Sept 2026) - a lighter monthly retainer to keep the recurring bill low relative to Herotel and support the case for the R334K build investment.</t>
         </is>
       </c>
     </row>

--- a/proposals/Barefoot_5Year_Business_Case.xlsx
+++ b/proposals/Barefoot_5Year_Business_Case.xlsx
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>7103</v>
+        <v>6818.4</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>8168</v>
+        <v>7841.16</v>
       </c>
       <c r="D16" s="6" t="n"/>
     </row>

--- a/proposals/Barefoot_5Year_Business_Case.xlsx
+++ b/proposals/Barefoot_5Year_Business_Case.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="1. Business Case" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2. CAPEX Build Cost" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2. Network Build Investment" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="3. Monthly Cost Comparison" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="4. 5-Year Cash Flow" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="5. Assumptions &amp; Scope" sheetId="5" state="visible" r:id="rId5"/>
@@ -47,34 +47,16 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="9"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="000000FF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <sz val="10"/>
     </font>
     <font>
@@ -91,7 +73,25 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <sz val="11"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -101,9 +101,9 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001F3864"/>
-      <sz val="10"/>
+      <i val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -137,12 +137,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E5395"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
+        <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -152,7 +147,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
+        <fgColor rgb="002E5395"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -182,51 +182,56 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -792,42 +797,42 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>Why build a private carrier-grade network instead of continuing to rent one, month after month, forever.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Prepared for: Barefoot Addo Elephant Lodge (Pty) Ltd owners (Port Elizabeth)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Prepared by: Gerhard Smit, CTTX Services (Pty) Ltd</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Date: 26 September 2026</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>The Simple Version</t>
         </is>
       </c>
     </row>
     <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>Right now the lodge pays a monthly bill to Herotel forever, for equipment it will never own, on a network it does not control. This proposal is the alternative: pay once to build a private network on your own engineered mast, then pay a much smaller monthly fee for the carrier link that feeds it. The network is built to run for 10 years, and CTTX supports it for that whole period.</t>
         </is>
@@ -836,122 +841,122 @@
     <row r="10"/>
     <row r="11"/>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Headline Numbers</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>One-time build cost (infrastructure, owned by the lodge)</t>
         </is>
       </c>
-      <c r="E14" s="28">
-        <f>'2. CAPEX Build Cost'!E40</f>
+      <c r="E14" s="31">
+        <f>'2. Network Build Investment'!C6</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>Current Herotel monthly bill (connectivity + rented Wi-Fi equipment)</t>
         </is>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="31">
         <f>'3. Monthly Cost Comparison'!C11</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>New monthly bill once built (Vodacom link + CTTX monitoring - recommended)</t>
         </is>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="31">
         <f>'3. Monthly Cost Comparison'!C26</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>Monthly saving once built</t>
         </is>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="31">
         <f>E15-E16</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Time to pay back the build cost</t>
         </is>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="32">
         <f>'4. 5-Year Cash Flow'!B28</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>Total saved over 5 years vs staying with Herotel</t>
         </is>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="31">
         <f>'4. 5-Year Cash Flow'!I30</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Why This Makes Sense Over 10 Years</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="29" t="inlineStr">
         <is>
           <t>1. The lodge currently pays for connectivity AND for the right to use someone else's Wi-Fi equipment, every month, indefinitely. Nothing is ever owned.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="26" t="inlineStr">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t>2. The existing backhaul radios are mounted on a leaning gum pole - not an engineered structure. That is a physical failure risk, separate from the cost problem.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="29" t="inlineStr">
         <is>
           <t>3. Building a private network converts a forever-rising monthly rental into a one-time build cost plus a much smaller ongoing carrier fee for just the connectivity - the Wi-Fi equipment, the mast, and the solar power all become the lodge's own asset.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="A25" s="29" t="inlineStr">
         <is>
           <t>4. CTTX designs, builds, and supports this network for an expected 10-year working life - see tab 5 for what that support includes and excludes.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="A26" s="29" t="inlineStr">
         <is>
           <t>5. See tab 4 for the year-by-year numbers: the build cost is recovered from the monthly saving within the payback period shown above, and every month after that is money the lodge keeps instead of sending to a telecoms reseller.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>Full cost detail: tab 2 (build cost), tab 3 (monthly comparison), tab 4 (5-year cash flow), tab 5 (assumptions - read this before trusting any number on this page).</t>
         </is>
@@ -988,625 +993,662 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>One-Time Build Cost (CAPEX)</t>
+          <t>Network Build Investment</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>All prices exclude VAT unless marked. Source: Duxbury Networking Quote DUX00455421 v2 + CTTX rate card + CTTX labour estimate.</t>
+          <t>Complete private wireless network - design, hardware, mast, cabinet, solar power system, installation, commissioning, and handover.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Hardware BOM</t>
-        </is>
+          <t>Complete Network Build (Excl. VAT)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>308695.65</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>VAT (15%)</t>
+        </is>
+      </c>
+      <c r="C5" s="6">
+        <f>C4*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL BUILD INVESTMENT (Incl. VAT)</t>
+        </is>
+      </c>
+      <c r="C6" s="8">
+        <f>C4+C5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Complete Scope of Supply</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Everything below is included in the build investment above. No per-item pricing is shown - this is the full scope of what gets installed, not a costed bill of materials.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Unit Price</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Backhaul Base Station</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Cambium ePMP 4500L 5GHz AP, 2x2, AC PoE</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>8470</v>
-      </c>
-      <c r="E6" s="7">
-        <f>C6*D6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Sector Antenna</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>ePMP Sector Antenna 5GHz 90/120deg</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>3209</v>
-      </c>
-      <c r="E7" s="7">
-        <f>C7*D7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Subscriber Modules</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Cambium ePMP Force 4525L, 25dBi</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>2745</v>
-      </c>
-      <c r="E8" s="7">
-        <f>C8*D8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Indoor Access Points</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>DuxNet Wi-Fi 6 Ceiling AP, 1Gb WAN/LAN</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>1025</v>
-      </c>
-      <c r="E9" s="7">
-        <f>C9*D9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Outdoor Access Points</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>DuxNet Outdoor Dual-Band Wi-Fi 6 AP</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>1885</v>
-      </c>
-      <c r="E10" s="7">
-        <f>C10*D10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Network Switches</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>DuxNet 8-Port Gigabit PoE+ L2 Cloud Switch</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>1899</v>
-      </c>
-      <c r="E11" s="7">
-        <f>C11*D11</f>
-        <v/>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Hardware Subtotal</t>
-        </is>
-      </c>
-      <c r="E12" s="9">
-        <f>SUM(E6:E11)</f>
-        <v/>
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Wireless Network Equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Cambium ePMP 4500L 5GHz Base Station Access Point</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Outdoor Infrastructure &amp; Civil</t>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ePMP Sector Antenna, 5GHz, 90/120 degree</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Not standard rate-card items - priced as supplier/stock quotes specific to this site (per Gerhard, confirmed 25-26 Sept 2026).</t>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Cambium ePMP Force 4525L Subscriber Module, 25dBi</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Unit Price</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="n"/>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    DuxNet Wi-Fi 6 Indoor Ceiling Access Point</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>9m Steel Mast with Plinth, installed</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>CTTX second-hand stock; replaces existing gum-pole mount</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>38700</v>
-      </c>
-      <c r="E17" s="7">
-        <f>C17*D17</f>
-        <v/>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    DuxNet Outdoor Dual-Band Wi-Fi 6 Access Point</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Outdoor Cabinet</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>w/ MPPT Charge Controller &amp; Lithium Battery Switchgear</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>28670</v>
-      </c>
-      <c r="E18" s="7">
-        <f>C18*D18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Solar Panels</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Canadian Solar 680W Monocrystalline</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>2200</v>
-      </c>
-      <c r="E19" s="7">
-        <f>C19*D19</f>
-        <v/>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    DuxNet 8-Port Gigabit PoE+ L2 Cloud Switch</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Grid/Solar Inverter</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr"/>
-      <c r="C20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>2150</v>
-      </c>
-      <c r="E20" s="7">
-        <f>C20*D20</f>
-        <v/>
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Mast &amp; Foundation (Civil Works)</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Outdoor Cabling</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Mast-to-cabinet, WAN, AP runs (avg. 40m run - confirm at survey)</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="E21" s="7">
-        <f>C21*D21</f>
-        <v/>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    9m Galvanized Steel Lattice Mast</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Mounting Brackets &amp; Hardware</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Radio, AP, and solar mounts</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>450</v>
-      </c>
-      <c r="E22" s="7">
-        <f>C22*D22</f>
-        <v/>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Ready-mix concrete for foundation plinth</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>As required</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Infrastructure Subtotal</t>
-        </is>
-      </c>
-      <c r="E23" s="9">
-        <f>SUM(E17:E22)</f>
-        <v/>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Building sand</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>As required</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Stone / grit aggregate (19mm)</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>As required</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Labour</t>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Reinforcing steel (rebar) for foundation</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>As required</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Days/Units</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Rate</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="n"/>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Foundation shuttering / formwork</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>As required</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Site survey and design</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>1 day</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="7" t="n">
-        <v>4500</v>
-      </c>
-      <c r="E27" s="7">
-        <f>C27*D27</f>
-        <v/>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Holding-down bolts (cast into plinth)</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Installation (AP deployment, cabling, PoE, switch config)</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>2-tech team, 3 days</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>9000</v>
-      </c>
-      <c r="E28" s="7">
-        <f>C28*D28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Commissioning and testing</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>1 day</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="7" t="n">
-        <v>4500</v>
-      </c>
-      <c r="E29" s="7">
-        <f>C29*D29</f>
-        <v/>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Mast mounting brackets, U-bolts and clamps</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Documentation and handover</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>1 half-day</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>2250</v>
-      </c>
-      <c r="E30" s="7">
-        <f>C30*D30</f>
-        <v/>
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Power System (Solar &amp; Battery)</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Labour Subtotal</t>
-        </is>
-      </c>
-      <c r="E31" s="9">
-        <f>SUM(E27:E30)</f>
-        <v/>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Outdoor equipment cabinet (weatherproof, IP-rated)</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>Travel/accommodation not applied - day-trip distance from PE assumed; confirm at survey.</t>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    MPPT solar charge controller</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>Trenching: not applicable - wireless solution, no underground civil works required.</t>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Lithium battery bank and switchgear</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Canadian Solar 680W monocrystalline panel</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Project Total</t>
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Solar panel mounting frame and rails</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>Set</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>Subtotal (Hardware + Infrastructure + Labour)</t>
-        </is>
-      </c>
-      <c r="E36" s="11">
-        <f>E12+E23+E31</f>
-        <v/>
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Grid/solar inverter</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>Contingency</t>
-        </is>
-      </c>
-      <c r="D37" s="13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E37" s="14">
-        <f>E36*D37</f>
-        <v/>
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Solar combiner box</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>Project Total (Excl. VAT)</t>
-        </is>
-      </c>
-      <c r="E38" s="9">
-        <f>E36+E37</f>
-        <v/>
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    DC and AC circuit breakers / isolators</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>VAT</t>
-        </is>
-      </c>
-      <c r="D39" s="13" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E39" s="14">
-        <f>E38*D39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="inlineStr">
-        <is>
-          <t>TOTAL BUILD COST (Incl. VAT)</t>
-        </is>
-      </c>
-      <c r="E40" s="16">
-        <f>E38+E39</f>
-        <v/>
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    MC4 solar connectors</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Cabling &amp; Conduit</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Outdoor-rated shielded Ethernet cable (Cat6A)</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>As required</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    LMR-400 low-loss antenna feeder cable</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="inlineStr">
+        <is>
+          <t>As required</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Armored power cable</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="inlineStr">
+        <is>
+          <t>As required</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Solar DC cable</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="inlineStr">
+        <is>
+          <t>As required</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PVC conduit / cable trays</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
+          <t>As required</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Weatherproof cable glands and connectors</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Cable ties, cleats and management hardware</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>Earthing &amp; Lightning Protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Copper earthing rods</t>
+        </is>
+      </c>
+      <c r="D51" s="13" t="inlineStr">
+        <is>
+          <t>2+</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Earthing conductor cable (16mm²)</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>As required</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Earthing clamps and bonding hardware</t>
+        </is>
+      </c>
+      <c r="D53" s="13" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Mast lightning air terminal</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>Installation, Commissioning &amp; Handover</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Site survey and RF link design</t>
+        </is>
+      </c>
+      <c r="D57" s="13" t="inlineStr">
+        <is>
+          <t>Included</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Installation labour (2-technician team)</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>Included</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Network configuration (switches, APs, VLANs, security)</t>
+        </is>
+      </c>
+      <c r="D59" s="13" t="inlineStr">
+        <is>
+          <t>Included</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Commissioning and performance testing</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="inlineStr">
+        <is>
+          <t>Included</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Staff training</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="inlineStr">
+        <is>
+          <t>Included</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Documentation and handover pack</t>
+        </is>
+      </c>
+      <c r="D62" s="13" t="inlineStr">
+        <is>
+          <t>Included</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A14:F14"/>
+  <mergeCells count="51">
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A45:C45"/>
     <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1644,117 +1686,117 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Current: Herotel Business (what the lodge pays today)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Excl. VAT</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>Incl. VAT</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr"/>
+      <c r="D5" s="14" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Business WTTB 100 Mbps Symmetrical</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="16" t="n">
         <v>9999</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="16" t="n">
         <v>11498.85</v>
       </c>
-      <c r="D6" s="6" t="n"/>
+      <c r="D6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Static IP</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="16" t="n">
         <v>180</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="16" t="n">
         <v>207</v>
       </c>
-      <c r="D7" s="6" t="n"/>
+      <c r="D7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Huawei Wi-Fi 6 AP 362 (Managed-lite, 9x 24-month term)</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="16" t="n">
         <v>2061</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="16" t="n">
         <v>2370.15</v>
       </c>
-      <c r="D8" s="6" t="n"/>
+      <c r="D8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>HB Managed Wi-Fi (Lite) 0-5 (x2)</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="16" t="n">
         <v>298</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="16" t="n">
         <v>342.7</v>
       </c>
-      <c r="D9" s="6" t="n"/>
+      <c r="D9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Huawei Wi-Fi 6 AP 362 (Managed-lite, 14x 12-month term)</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="16" t="n">
         <v>3206</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="16" t="n">
         <v>3686.9</v>
       </c>
-      <c r="D10" s="6" t="n"/>
+      <c r="D10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Herotel Monthly Total (current)</t>
         </is>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="18">
         <f>SUM(B6:B10)</f>
         <v/>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="18">
         <f>SUM(C6:C10)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Proposed: Vodacom Business Connect via CTTX (carrier connectivity only)</t>
         </is>
@@ -1768,68 +1810,68 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>Excl. VAT</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>Incl. VAT</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr"/>
+      <c r="D15" s="14" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Vodacom Business Connect 100 Mbps (Monthly Recurring Charge)</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B16" s="16" t="n">
         <v>6818.4</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="16" t="n">
         <v>7841.16</v>
       </c>
-      <c r="D16" s="6" t="n"/>
+      <c r="D16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Once-off Connection Fee (NRC) - not monthly, shown for reference</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B17" s="16" t="n">
         <v>3130</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="16" t="n">
         <v>3599</v>
       </c>
-      <c r="D17" s="6" t="n"/>
+      <c r="D17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Vodacom-Only Monthly Total</t>
         </is>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="18">
         <f>B16</f>
         <v/>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="18">
         <f>C16</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Optional Add-On: CTTX Managed Service Retainer (recommended)</t>
         </is>
@@ -1843,77 +1885,77 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>Excl. VAT</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>Incl. VAT</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr"/>
+      <c r="D22" s="14" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Managed Service Retainer (remote monitoring, maintenance, support)</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n">
+      <c r="B23" s="16" t="n">
         <v>1500</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="16" t="n">
         <v>1725</v>
       </c>
-      <c r="D23" s="6" t="n"/>
+      <c r="D23" s="15" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Recommended Path: Vodacom + Managed Retainer</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Recommended Monthly Total (Vodacom + Retainer)</t>
         </is>
       </c>
-      <c r="B26" s="9">
+      <c r="B26" s="18">
         <f>B16+B23</f>
         <v/>
       </c>
-      <c r="C26" s="16">
+      <c r="C26" s="8">
         <f>C16+C23</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>Monthly saving vs Herotel (recommended path, incl. VAT)</t>
         </is>
       </c>
-      <c r="C27" s="18">
+      <c r="C27" s="19">
         <f>C11-C26</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>Monthly saving vs Herotel (Vodacom-only, self-maintained, incl. VAT)</t>
         </is>
       </c>
-      <c r="C28" s="18">
+      <c r="C28" s="19">
         <f>C11-C18</f>
         <v/>
       </c>
@@ -1967,414 +2009,414 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Annual escalation rate (applied to both Herotel and Vodacom monthly fees)</t>
         </is>
       </c>
-      <c r="B4" s="13" t="n">
+      <c r="B4" s="20" t="n">
         <v>0.08</v>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="21" t="inlineStr">
         <is>
           <t>&lt;- editable assumption; see tab 5 for why 8% was used</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
+      <c r="B6" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="19" t="n">
+      <c r="G6" s="11" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Path A: Stay with Herotel (do nothing)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Herotel monthly bill (escalated)</t>
         </is>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="22">
         <f>'3. Monthly Cost Comparison'!$C$11</f>
         <v/>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="22">
         <f>B8*(1+$B$4)</f>
         <v/>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="22">
         <f>C8*(1+$B$4)</f>
         <v/>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="22">
         <f>D8*(1+$B$4)</f>
         <v/>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="22">
         <f>E8*(1+$B$4)</f>
         <v/>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="22">
         <f>F8*(1+$B$4)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Herotel annual cost</t>
         </is>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="22">
         <f>B8*12</f>
         <v/>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="22">
         <f>C8*12</f>
         <v/>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="22">
         <f>D8*12</f>
         <v/>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="22">
         <f>E8*12</f>
         <v/>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="22">
         <f>F8*12</f>
         <v/>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="22">
         <f>G8*12</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Herotel cumulative cost</t>
         </is>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="18">
         <f>B9</f>
         <v/>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="18">
         <f>B10+C9</f>
         <v/>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="18">
         <f>C10+D9</f>
         <v/>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="18">
         <f>D10+E9</f>
         <v/>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="18">
         <f>E10+F9</f>
         <v/>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="18">
         <f>F10+G9</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Path B: Build the CTTX private network (recommended - Vodacom + Managed Retainer)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Build cost (one-time, Year 0 only)</t>
         </is>
       </c>
-      <c r="B13" s="20">
-        <f>'2. CAPEX Build Cost'!$E$40</f>
-        <v/>
-      </c>
-      <c r="C13" s="20" t="n">
+      <c r="B13" s="22">
+        <f>'2. Network Build Investment'!$C$6</f>
+        <v/>
+      </c>
+      <c r="C13" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="D13" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E13" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="20" t="n">
+      <c r="F13" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="20" t="n">
+      <c r="G13" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Vodacom once-off connection fee (Year 0 only)</t>
         </is>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="22">
         <f>'3. Monthly Cost Comparison'!$C$17</f>
         <v/>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="20" t="n">
+      <c r="F14" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="20" t="n">
+      <c r="G14" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>CTTX monthly recurring (Vodacom + Retainer, escalated)</t>
         </is>
       </c>
-      <c r="B15" s="20" t="n">
+      <c r="B15" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="22">
         <f>'3. Monthly Cost Comparison'!$C$26</f>
         <v/>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="22">
         <f>C15*(1+$B$4)</f>
         <v/>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="22">
         <f>D15*(1+$B$4)</f>
         <v/>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="22">
         <f>E15*(1+$B$4)</f>
         <v/>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="22">
         <f>F15*(1+$B$4)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>CTTX annual recurring cost</t>
         </is>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="22">
         <f>B15*12</f>
         <v/>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="22">
         <f>C15*12</f>
         <v/>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="22">
         <f>D15*12</f>
         <v/>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="22">
         <f>E15*12</f>
         <v/>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="22">
         <f>F15*12</f>
         <v/>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="22">
         <f>G15*12</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>CTTX cumulative cost</t>
         </is>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="18">
         <f>B13+B14+B16</f>
         <v/>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="18">
         <f>B17+C16</f>
         <v/>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="18">
         <f>C17+D16</f>
         <v/>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="18">
         <f>D17+E16</f>
         <v/>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="18">
         <f>E17+F16</f>
         <v/>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="18">
         <f>F17+G16</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Cumulative Savings (Path A minus Path B)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Cumulative savings from building (negative = still paying off the build)</t>
         </is>
       </c>
-      <c r="B20" s="21">
+      <c r="B20" s="23">
         <f>B10-B17</f>
         <v/>
       </c>
-      <c r="C20" s="21">
+      <c r="C20" s="23">
         <f>C10-C17</f>
         <v/>
       </c>
-      <c r="D20" s="21">
+      <c r="D20" s="23">
         <f>D10-D17</f>
         <v/>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="23">
         <f>E10-E17</f>
         <v/>
       </c>
-      <c r="F20" s="21">
+      <c r="F20" s="23">
         <f>F10-F17</f>
         <v/>
       </c>
-      <c r="G20" s="21">
+      <c r="G20" s="23">
         <f>G10-G17</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Payback Calculation</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Last year cumulative savings still negative or zero (position in range)</t>
         </is>
       </c>
-      <c r="B23" s="22">
+      <c r="B23" s="24">
         <f>MATCH(0,B20:G20,1)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>That year number</t>
         </is>
       </c>
-      <c r="B24" s="22">
+      <c r="B24" s="24">
         <f>INDEX(B6:G6,B23)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Cumulative savings at that year</t>
         </is>
       </c>
-      <c r="B25" s="20">
+      <c r="B25" s="22">
         <f>INDEX(B20:G20,B23)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Cumulative savings the following year</t>
         </is>
       </c>
-      <c r="B26" s="20">
+      <c r="B26" s="22">
         <f>INDEX(B20:G20,B23+1)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>Payback point (years, decimal)</t>
         </is>
       </c>
-      <c r="B27" s="23">
+      <c r="B27" s="25">
         <f>B24+(-B25)/(B26-B25)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>Payback point (plain English)</t>
         </is>
       </c>
-      <c r="B28" s="24">
+      <c r="B28" s="26">
         <f>TEXT(INT(B27),"0")&amp;" years, "&amp;TEXT(ROUND((B27-INT(B27))*12,0),"0")&amp;" months"</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>Total 5-year saving vs Herotel (recommended path)</t>
         </is>
       </c>
-      <c r="I30" s="25">
+      <c r="I30" s="27">
         <f>G20</f>
         <v/>
       </c>
@@ -2400,7 +2442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2416,221 +2458,204 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Financial Assumptions</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Annual price escalation (Herotel and Vodacom)</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>8% p.a.</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>Not confirmed by either party - a typical CPI-linked telecom escalation in South Africa. Editable on tab 4; change it and every formula recalculates.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Contingency on build cost</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="C6" s="26" t="inlineStr">
-        <is>
-          <t>Standard CTTX estimating practice for a project at this stage (pre-final-survey).</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>VAT rate</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="inlineStr">
+        <is>
+          <t>Current South African VAT rate.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>VAT rate</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="C7" s="26" t="inlineStr">
-        <is>
-          <t>Current South African VAT rate.</t>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Managed Service Retainer</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>R1,500/month excl. VAT</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t>Set by Gerhard (26 Sept 2026) - a lighter monthly retainer to keep the recurring bill low relative to Herotel and support the case for the build investment.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Managed Service Retainer</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>R1,500/month excl. VAT</t>
-        </is>
-      </c>
-      <c r="C8" s="26" t="inlineStr">
-        <is>
-          <t>Set by Gerhard (26 Sept 2026) - a lighter monthly retainer to keep the recurring bill low relative to Herotel and support the case for the R334K build investment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Contract term - Vodacom Business Connect</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>24 months</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Standard Vodacom Business Connect contract term. The network's physical life (10 years) is longer than this contract term - Vodacom connectivity is expected to be renewed at then-current rates.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Design Assumptions</t>
         </is>
       </c>
     </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>Single 9m mast carrying two 90-degree sector antennas (confirmed by Gerhard, 26 Sept 2026) - replaces the lodge's existing leaning gum-pole mount. This is NOT a two-site build; earlier drafts of this costing incorrectly read the field survey's two radio labels as two separate physical locations before this was corrected.</t>
+        </is>
+      </c>
+    </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>Single 9m mast carrying two 90-degree sector antennas (confirmed by Gerhard, 26 Sept 2026) - replaces the lodge's existing leaning gum-pole mount. This is NOT a two-site build; earlier drafts of this costing incorrectly read the field survey's two radio labels as two separate physical locations before this was corrected.</t>
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>Line-of-sight confirmed for all 28 subscriber links by Abel Ringisai's field RF survey (KML export, 22 Sept 2026).</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
-        <is>
-          <t>Line-of-sight confirmed for all 28 subscriber links by Abel Ringisai's field RF survey (KML export, 22 Sept 2026).</t>
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>The longest links (1.7km-3.0km, to the staff village and Director's House) sit at the edge of the serving sector's range and still need a link-budget check to confirm they sustain full 100 Mbps symmetrical - flagged, not yet resolved.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="26" t="inlineStr">
-        <is>
-          <t>The longest links (1.7km-3.0km, to the staff village and Director's House) sit at the edge of the serving sector's range and still need a link-budget check to confirm they sustain full 100 Mbps symmetrical - flagged, not yet resolved.</t>
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>Cable run priced at an average 40m per run - to be confirmed once exact distances are measured on site.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>Cable run priced at an average 40m per run - to be confirmed once exact distances are measured on site.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>Vodacom Business Connect feasibility for this specific site has not yet been formally submitted/approved.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>What's Included in the 10-Year Support</t>
         </is>
       </c>
     </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>Years 1-3: monthly remote monitoring, quarterly on-site maintenance, 24/7 emergency support, proactive performance reporting, warranty-covered equipment troubleshooting/replacement.</t>
+        </is>
+      </c>
+    </row>
     <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="26" t="inlineStr">
-        <is>
-          <t>Years 1-3: monthly remote monitoring, quarterly on-site maintenance, 24/7 emergency support, proactive performance reporting, warranty-covered equipment troubleshooting/replacement.</t>
+      <c r="A19" s="29" t="inlineStr">
+        <is>
+          <t>Years 4-10: ongoing remote monitoring, annual on-site maintenance/assessment, 24/7 support continuation, planned technology refresh, performance reporting.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="26" t="inlineStr">
-        <is>
-          <t>Years 4-10: ongoing remote monitoring, annual on-site maintenance/assessment, 24/7 support continuation, planned technology refresh, performance reporting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t>Throughout: no vendor lock-in on the owned hardware, scalability support, staff training and documentation.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>What's Excluded / Not Yet Priced</t>
         </is>
       </c>
     </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>Major component replacement (Lithium battery bank, inverter) near the end of the 10-year term - typical service life for this equipment is 8-10 years, so a replacement reserve may be needed in years 8-10 and is not included in the build cost above.</t>
+        </is>
+      </c>
+    </row>
     <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="26" t="inlineStr">
-        <is>
-          <t>Major component replacement (Lithium battery bank, inverter) near the end of the 10-year term - typical service life for this equipment is 8-10 years, so a replacement reserve may be needed in years 8-10 and is not included in the build cost above.</t>
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>Trenching or underground civil works (none required - this is a wireless solution).</t>
         </is>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="26" t="inlineStr">
-        <is>
-          <t>Trenching or underground civil works (none required - this is a wireless solution).</t>
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>CCTV cameras, POS hardware, or other endpoint devices not listed in the hardware BOM.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="26" t="inlineStr">
-        <is>
-          <t>CCTV cameras, POS hardware, or other endpoint devices not listed in the hardware BOM.</t>
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>Travel/accommodation beyond a day-trip assumption from Port Elizabeth (~1h45 drive) - to be confirmed if overnight stays are required during the 3-day install.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="26" t="inlineStr">
-        <is>
-          <t>Travel/accommodation beyond a day-trip assumption from Port Elizabeth (~1h45 drive) - to be confirmed if overnight stays are required during the 3-day install.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="26" t="inlineStr">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t>Any scope beyond the confirmed coverage zones (28 subscriber sites) without a signed change order.</t>
         </is>
@@ -2638,19 +2663,19 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A10:C10"/>
     <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A13:C13"/>
     <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A13:C13"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A16:C16"/>
     <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A17:C17"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A24:C24"/>

--- a/proposals/Barefoot_5Year_Business_Case.xlsx
+++ b/proposals/Barefoot_5Year_Business_Case.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="&quot;R&quot;#,##0.00;(&quot;R&quot;#,##0.00);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -108,6 +108,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00008000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="11"/>
     </font>
@@ -182,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -217,21 +223,26 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="15" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -778,7 +789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -797,7 +808,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>Why build a private carrier-grade network instead of continuing to rent one, month after month, forever.</t>
         </is>
@@ -832,7 +843,7 @@
       </c>
     </row>
     <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Right now the lodge pays a monthly bill to Herotel forever, for equipment it will never own, on a network it does not control. This proposal is the alternative: pay once to build a private network on your own engineered mast, then pay a much smaller monthly fee for the carrier link that feeds it. The network is built to run for 10 years, and CTTX supports it for that whole period.</t>
         </is>
@@ -853,7 +864,7 @@
           <t>One-time build cost (infrastructure, owned by the lodge)</t>
         </is>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="33">
         <f>'2. Network Build Investment'!C6</f>
         <v/>
       </c>
@@ -864,7 +875,7 @@
           <t>Current Herotel monthly bill (connectivity + rented Wi-Fi equipment)</t>
         </is>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="33">
         <f>'3. Monthly Cost Comparison'!C11</f>
         <v/>
       </c>
@@ -875,7 +886,7 @@
           <t>New monthly bill once built (Vodacom link + CTTX monitoring - recommended)</t>
         </is>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="33">
         <f>'3. Monthly Cost Comparison'!C26</f>
         <v/>
       </c>
@@ -886,7 +897,7 @@
           <t>Monthly saving once built</t>
         </is>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="33">
         <f>E15-E16</f>
         <v/>
       </c>
@@ -897,8 +908,8 @@
           <t>Time to pay back the build cost</t>
         </is>
       </c>
-      <c r="E18" s="32">
-        <f>'4. 5-Year Cash Flow'!B28</f>
+      <c r="E18" s="34">
+        <f>'4. 5-Year Cash Flow'!B29</f>
         <v/>
       </c>
     </row>
@@ -908,80 +919,92 @@
           <t>Total saved over 5 years vs staying with Herotel</t>
         </is>
       </c>
-      <c r="E19" s="31">
-        <f>'4. 5-Year Cash Flow'!I30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="E19" s="33">
+        <f>'4. 5-Year Cash Flow'!I31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>5-Year Return on Investment</t>
+        </is>
+      </c>
+      <c r="E20" s="35">
+        <f>'4. 5-Year Cash Flow'!I32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Why This Makes Sense Over 10 Years</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="29" t="inlineStr">
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t>1. The lodge currently pays for connectivity AND for the right to use someone else's Wi-Fi equipment, every month, indefinitely. Nothing is ever owned.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="29" t="inlineStr">
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>2. The existing backhaul radios are mounted on a leaning gum pole - not an engineered structure. That is a physical failure risk, separate from the cost problem.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="29" t="inlineStr">
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>3. Building a private network converts a forever-rising monthly rental into a one-time build cost plus a much smaller ongoing carrier fee for just the connectivity - the Wi-Fi equipment, the mast, and the solar power all become the lodge's own asset.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="29" t="inlineStr">
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="31" t="inlineStr">
         <is>
           <t>4. CTTX designs, builds, and supports this network for an expected 10-year working life - see tab 5 for what that support includes and excludes.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="29" t="inlineStr">
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>5. See tab 4 for the year-by-year numbers: the build cost is recovered from the monthly saving within the payback period shown above, and every month after that is money the lodge keeps instead of sending to a telecoms reseller.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="21" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>Full cost detail: tab 2 (build cost), tab 3 (monthly comparison), tab 4 (5-year cash flow), tab 5 (assumptions - read this before trusting any number on this page).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A24:F24"/>
+  <mergeCells count="19">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A9:F11"/>
-    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A13:F13"/>
     <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A9:F11"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1981,7 +2004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2337,99 +2360,141 @@
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>Return on Investment (cumulative savings vs. Herotel, as % of total upfront cash outlay)</t>
+        </is>
+      </c>
+      <c r="B21" s="24">
+        <f>B20/$B$17</f>
+        <v/>
+      </c>
+      <c r="C21" s="24">
+        <f>C20/$B$17</f>
+        <v/>
+      </c>
+      <c r="D21" s="24">
+        <f>D20/$B$17</f>
+        <v/>
+      </c>
+      <c r="E21" s="24">
+        <f>E20/$B$17</f>
+        <v/>
+      </c>
+      <c r="F21" s="24">
+        <f>F20/$B$17</f>
+        <v/>
+      </c>
+      <c r="G21" s="24">
+        <f>G20/$B$17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>Payback Calculation</t>
         </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Last year cumulative savings still negative or zero (position in range)</t>
-        </is>
-      </c>
-      <c r="B23" s="24">
-        <f>MATCH(0,B20:G20,1)</f>
-        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>That year number</t>
-        </is>
-      </c>
-      <c r="B24" s="24">
-        <f>INDEX(B6:G6,B23)</f>
+          <t>Last year cumulative savings still negative or zero (position in range)</t>
+        </is>
+      </c>
+      <c r="B24" s="25">
+        <f>MATCH(0,B20:G20,1)</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Cumulative savings at that year</t>
-        </is>
-      </c>
-      <c r="B25" s="22">
-        <f>INDEX(B20:G20,B23)</f>
+          <t>That year number</t>
+        </is>
+      </c>
+      <c r="B25" s="25">
+        <f>INDEX(B6:G6,B24)</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Cumulative savings the following year</t>
+          <t>Cumulative savings at that year</t>
         </is>
       </c>
       <c r="B26" s="22">
-        <f>INDEX(B20:G20,B23+1)</f>
+        <f>INDEX(B20:G20,B24)</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
+          <t>Cumulative savings the following year</t>
+        </is>
+      </c>
+      <c r="B27" s="22">
+        <f>INDEX(B20:G20,B24+1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
           <t>Payback point (years, decimal)</t>
         </is>
       </c>
-      <c r="B27" s="25">
-        <f>B24+(-B25)/(B26-B25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="B28" s="26">
+        <f>B25+(-B26)/(B27-B26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>Payback point (plain English)</t>
         </is>
       </c>
-      <c r="B28" s="26">
-        <f>TEXT(INT(B27),"0")&amp;" years, "&amp;TEXT(ROUND((B27-INT(B27))*12,0),"0")&amp;" months"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="B29" s="27">
+        <f>TEXT(INT(B28),"0")&amp;" years, "&amp;TEXT(ROUND((B28-INT(B28))*12,0),"0")&amp;" months"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>Total 5-year saving vs Herotel (recommended path)</t>
         </is>
       </c>
-      <c r="I30" s="27">
+      <c r="I31" s="28">
         <f>G20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>5-Year ROI (total saving as % of total upfront cash outlay)</t>
+        </is>
+      </c>
+      <c r="I32" s="29">
+        <f>G21</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A22:G22"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="C4:H4"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2465,12 +2530,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="B4" s="28" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -2492,7 +2557,7 @@
           <t>8% p.a.</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
         <is>
           <t>Not confirmed by either party - a typical CPI-linked telecom escalation in South Africa. Editable on tab 4; change it and every formula recalculates.</t>
         </is>
@@ -2509,7 +2574,7 @@
           <t>15%</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t>Current South African VAT rate.</t>
         </is>
@@ -2526,7 +2591,7 @@
           <t>R1,500/month excl. VAT</t>
         </is>
       </c>
-      <c r="C7" s="29" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>Set by Gerhard (26 Sept 2026) - a lighter monthly retainer to keep the recurring bill low relative to Herotel and support the case for the build investment.</t>
         </is>
@@ -2543,7 +2608,7 @@
           <t>24 months</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
         <is>
           <t>Standard Vodacom Business Connect contract term. The network's physical life (10 years) is longer than this contract term - Vodacom connectivity is expected to be renewed at then-current rates.</t>
         </is>
@@ -2557,35 +2622,35 @@
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>Single 9m mast carrying two 90-degree sector antennas (confirmed by Gerhard, 26 Sept 2026) - replaces the lodge's existing leaning gum-pole mount. This is NOT a two-site build; earlier drafts of this costing incorrectly read the field survey's two radio labels as two separate physical locations before this was corrected.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>Line-of-sight confirmed for all 28 subscriber links by Abel Ringisai's field RF survey (KML export, 22 Sept 2026).</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>The longest links (1.7km-3.0km, to the staff village and Director's House) sit at the edge of the serving sector's range and still need a link-budget check to confirm they sustain full 100 Mbps symmetrical - flagged, not yet resolved.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="29" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>Cable run priced at an average 40m per run - to be confirmed once exact distances are measured on site.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="29" t="inlineStr">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>Vodacom Business Connect feasibility for this specific site has not yet been formally submitted/approved.</t>
         </is>
@@ -2599,21 +2664,21 @@
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="29" t="inlineStr">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>Years 1-3: monthly remote monitoring, quarterly on-site maintenance, 24/7 emergency support, proactive performance reporting, warranty-covered equipment troubleshooting/replacement.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>Years 4-10: ongoing remote monitoring, annual on-site maintenance/assessment, 24/7 support continuation, planned technology refresh, performance reporting.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>Throughout: no vendor lock-in on the owned hardware, scalability support, staff training and documentation.</t>
         </is>
@@ -2627,35 +2692,35 @@
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="29" t="inlineStr">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t>Major component replacement (Lithium battery bank, inverter) near the end of the 10-year term - typical service life for this equipment is 8-10 years, so a replacement reserve may be needed in years 8-10 and is not included in the build cost above.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="29" t="inlineStr">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>Trenching or underground civil works (none required - this is a wireless solution).</t>
         </is>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="29" t="inlineStr">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>CCTV cameras, POS hardware, or other endpoint devices not listed in the hardware BOM.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="29" t="inlineStr">
+      <c r="A26" s="31" t="inlineStr">
         <is>
           <t>Travel/accommodation beyond a day-trip assumption from Port Elizabeth (~1h45 drive) - to be confirmed if overnight stays are required during the 3-day install.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="29" t="inlineStr">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>Any scope beyond the confirmed coverage zones (28 subscriber sites) without a signed change order.</t>
         </is>

--- a/proposals/Barefoot_5Year_Business_Case.xlsx
+++ b/proposals/Barefoot_5Year_Business_Case.xlsx
@@ -2605,12 +2605,12 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>24 months</t>
+          <t>36 months</t>
         </is>
       </c>
       <c r="C8" s="31" t="inlineStr">
         <is>
-          <t>Standard Vodacom Business Connect contract term. The network's physical life (10 years) is longer than this contract term - Vodacom connectivity is expected to be renewed at then-current rates.</t>
+          <t>Set by Gerhard (26 Sept 2026) - the deal is structured as a 36-month agreement. NOT YET CONFIRMED: the Notion pricing master's MRC figure used in this model is the standard 24-month rate; Vodacom's actual 36-month rate for Business Connect has not been checked and may differ.</t>
         </is>
       </c>
     </row>

--- a/proposals/Barefoot_5Year_Business_Case.xlsx
+++ b/proposals/Barefoot_5Year_Business_Case.xlsx
@@ -1828,7 +1828,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Uncontended (1:1), Uncapped, Unshaped, No FUP, Symmetrical, Business SLA, Huawei router included, 1 static IP standard. 24-month contract. Subject to feasibility confirmation.</t>
+          <t>Uncontended (1:1), Uncapped, Unshaped, No FUP, Symmetrical, Business SLA, LTE backup, Huawei router included, 1 static IP standard. 36-month contract. Subject to feasibility confirmation.</t>
         </is>
       </c>
     </row>
@@ -1853,14 +1853,14 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>Vodacom Business Connect 100 Mbps (Monthly Recurring Charge)</t>
+          <t>Vodacom Business Connect 100 Mbps (Monthly Recurring Charge, 36-month term)</t>
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>6818.4</v>
+        <v>6281.74</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>7841.16</v>
+        <v>7224</v>
       </c>
       <c r="D16" s="15" t="n"/>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="C8" s="31" t="inlineStr">
         <is>
-          <t>Set by Gerhard (26 Sept 2026) - the deal is structured as a 36-month agreement. NOT YET CONFIRMED: the Notion pricing master's MRC figure used in this model is the standard 24-month rate; Vodacom's actual 36-month rate for Business Connect has not been checked and may differ.</t>
+          <t>Confirmed 28 Sept 2026 against the CTTX Vodacom Reseller price book (Duane Forlee, Vodacom, 29 May 2026): the 36-month rate is slightly lower than 24-month. Monthly figure in this model is the confirmed 36-month client price at CTTX's standard 20% markup.</t>
         </is>
       </c>
     </row>

--- a/proposals/Barefoot_5Year_Business_Case.xlsx
+++ b/proposals/Barefoot_5Year_Business_Case.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="1. Business Case" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2. Network Build Investment" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3. Monthly Cost Comparison" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4. 5-Year Cash Flow" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5. Assumptions &amp; Scope" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2. Network Build Investment" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3. Monthly Cost Comparison" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="4. 5-Year Cash Flow" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5. Assumptions &amp; Scope" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -188,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -227,6 +228,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="16" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="16" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -323,6 +325,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
   <chart>
     <title>
       <tx>
@@ -808,7 +811,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="32" t="inlineStr">
+      <c r="A2" s="33" t="inlineStr">
         <is>
           <t>Why build a private carrier-grade network instead of continuing to rent one, month after month, forever.</t>
         </is>
@@ -843,7 +846,7 @@
       </c>
     </row>
     <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Right now the lodge pays a monthly bill to Herotel forever, for equipment it will never own, on a network it does not control. This proposal is the alternative: pay once to build a private network on your own engineered mast, then pay a much smaller monthly fee for the carrier link that feeds it. The network is built to run for 10 years, and CTTX supports it for that whole period.</t>
         </is>
@@ -864,7 +867,7 @@
           <t>One-time build cost (infrastructure, owned by the lodge)</t>
         </is>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="34">
         <f>'2. Network Build Investment'!C6</f>
         <v/>
       </c>
@@ -875,7 +878,7 @@
           <t>Current Herotel monthly bill (connectivity + rented Wi-Fi equipment)</t>
         </is>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="34">
         <f>'3. Monthly Cost Comparison'!C11</f>
         <v/>
       </c>
@@ -886,7 +889,7 @@
           <t>New monthly bill once built (Vodacom link + CTTX monitoring - recommended)</t>
         </is>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="34">
         <f>'3. Monthly Cost Comparison'!C26</f>
         <v/>
       </c>
@@ -897,7 +900,7 @@
           <t>Monthly saving once built</t>
         </is>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="34">
         <f>E15-E16</f>
         <v/>
       </c>
@@ -908,7 +911,7 @@
           <t>Time to pay back the build cost</t>
         </is>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="35">
         <f>'4. 5-Year Cash Flow'!B29</f>
         <v/>
       </c>
@@ -919,8 +922,8 @@
           <t>Total saved over 5 years vs staying with Herotel</t>
         </is>
       </c>
-      <c r="E19" s="33">
-        <f>'4. 5-Year Cash Flow'!I31</f>
+      <c r="E19" s="34">
+        <f>'4. 5-Year Cash Flow'!I36</f>
         <v/>
       </c>
     </row>
@@ -930,8 +933,8 @@
           <t>5-Year Return on Investment</t>
         </is>
       </c>
-      <c r="E20" s="35">
-        <f>'4. 5-Year Cash Flow'!I32</f>
+      <c r="E20" s="36">
+        <f>'4. 5-Year Cash Flow'!I37</f>
         <v/>
       </c>
     </row>
@@ -943,35 +946,35 @@
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="31" t="inlineStr">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>1. The lodge currently pays for connectivity AND for the right to use someone else's Wi-Fi equipment, every month, indefinitely. Nothing is ever owned.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="31" t="inlineStr">
+      <c r="A24" s="32" t="inlineStr">
         <is>
           <t>2. The existing backhaul radios are mounted on a leaning gum pole - not an engineered structure. That is a physical failure risk, separate from the cost problem.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="31" t="inlineStr">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t>3. Building a private network converts a forever-rising monthly rental into a one-time build cost plus a much smaller ongoing carrier fee for just the connectivity - the Wi-Fi equipment, the mast, and the solar power all become the lodge's own asset.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="31" t="inlineStr">
+      <c r="A26" s="32" t="inlineStr">
         <is>
           <t>4. CTTX designs, builds, and supports this network for an expected 10-year working life - see tab 5 for what that support includes and excludes.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="31" t="inlineStr">
+      <c r="A27" s="32" t="inlineStr">
         <is>
           <t>5. See tab 4 for the year-by-year numbers: the build cost is recovered from the monthly saving within the payback period shown above, and every month after that is money the lodge keeps instead of sending to a telecoms reseller.</t>
         </is>
@@ -1016,8 +1019,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D62"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
@@ -1677,14 +1693,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
@@ -1998,14 +2014,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
@@ -2024,17 +2040,17 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="40" customHeight="1">
+    <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Year 0 = build year (deposit and construction). Years 1-5 are projected here deliberately, rather than compounding the escalation assumption out to a full decade. The network's engineered/expected working life is longer (see tab 5) and CTTX's support commitment runs 10 years - this cash flow is the near-term financial case, not a claim about how long the equipment lasts. All figures incl. VAT.</t>
+          <t>Year 0 = the day the build is paid for. Both paths start paying their monthly bills from month 1, so the two lines are compared on the same clock: the current provider is NOT charged a year of bills before the build, and CTTX is NOT given a free year. Years 1-5 are projected here deliberately, rather than compounding the escalation assumption out to a full decade. The network's engineered/expected working life is longer (see tab 5) and CTTX's support commitment runs 10 years - this cash flow is the near-term financial case, not a claim about how long the equipment lasts. All figures incl. VAT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>Annual escalation rate (applied to both Herotel and Vodacom monthly fees)</t>
+          <t>Annual escalation rate (current provider from year 2; CTTX only after the 36-month locked term, i.e. from year 4)</t>
         </is>
       </c>
       <c r="B4" s="20" t="n">
@@ -2081,15 +2097,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Herotel monthly bill (escalated)</t>
-        </is>
-      </c>
-      <c r="B8" s="22">
+          <t>Herotel monthly bill (year 1 = today's bill; escalated from year 2)</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="22">
         <f>'3. Monthly Cost Comparison'!$C$11</f>
-        <v/>
-      </c>
-      <c r="C8" s="22">
-        <f>B8*(1+$B$4)</f>
         <v/>
       </c>
       <c r="D8" s="22">
@@ -2233,7 +2248,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>CTTX monthly recurring (Vodacom + Retainer, escalated)</t>
+          <t>CTTX monthly recurring (Vodacom + Retainer; locked for the 36-month term, escalated from year 4)</t>
         </is>
       </c>
       <c r="B15" s="22" t="n">
@@ -2244,11 +2259,11 @@
         <v/>
       </c>
       <c r="D15" s="22">
-        <f>C15*(1+$B$4)</f>
+        <f>C15</f>
         <v/>
       </c>
       <c r="E15" s="22">
-        <f>D15*(1+$B$4)</f>
+        <f>D15</f>
         <v/>
       </c>
       <c r="F15" s="22">
@@ -2465,29 +2480,70 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Over the 36-month agreement term (end of year 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Paid to Herotel over 36 months (if nothing changes)</t>
+        </is>
+      </c>
+      <c r="B32" s="22">
+        <f>E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Paid on the CTTX path over 36 months (build + connection fee + 36 monthly bills)</t>
+        </is>
+      </c>
+      <c r="B33" s="22">
+        <f>E17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>Difference over the term (positive = CTTX path cheaper) - and the lodge owns the network at the end</t>
+        </is>
+      </c>
+      <c r="B34" s="28">
+        <f>E20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>Total 5-year saving vs Herotel (recommended path)</t>
         </is>
       </c>
-      <c r="I31" s="28">
+      <c r="I36" s="29">
         <f>G20</f>
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>5-Year ROI (total saving as % of total upfront cash outlay)</t>
         </is>
       </c>
-      <c r="I32" s="29">
+      <c r="I37" s="30">
         <f>G21</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="C4:H4"/>
@@ -2501,14 +2557,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -2530,12 +2586,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -2549,178 +2605,212 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Annual price escalation (Herotel and Vodacom)</t>
+          <t>Annual price escalation - current provider (Herotel)</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>8% p.a.</t>
-        </is>
-      </c>
-      <c r="C5" s="31" t="inlineStr">
-        <is>
-          <t>Not confirmed by either party - a typical CPI-linked telecom escalation in South Africa. Editable on tab 4; change it and every formula recalculates.</t>
+          <t>8% p.a. from year 2</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="inlineStr">
+        <is>
+          <t>Not confirmed by Herotel - a typical CPI-linked telecom escalation in South Africa. Editable on tab 4; change it and every formula recalculates. Set it to 0% and payback moves from 2 years 10 months to 3 years 4 months.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>VAT rate</t>
+          <t>Price escalation - CTTX path (Vodacom + retainer)</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="C6" s="31" t="inlineStr">
-        <is>
-          <t>Current South African VAT rate.</t>
+          <t>0% for the 36-month term, then 8% p.a.</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="inlineStr">
+        <is>
+          <t>The Vodacom Business Connect 36-month contract price and the CTTX retainer are fixed for the term of the agreement. The same 8% is applied after the term ends (years 4-5) so the CTTX path is not flattered.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Managed Service Retainer</t>
+          <t>Timing of the comparison</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>R1,500/month excl. VAT</t>
-        </is>
-      </c>
-      <c r="C7" s="31" t="inlineStr">
-        <is>
-          <t>Set by Gerhard (26 Sept 2026) - a lighter monthly retainer to keep the recurring bill low relative to Herotel and support the case for the build investment.</t>
+          <t>Both paths start at month 1</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="inlineStr">
+        <is>
+          <t>Year 0 is the build payment only. Neither path is charged any monthly bill in year 0 - an earlier version of this model charged Herotel a full year before the build and gave the CTTX path none, which overstated the case. Corrected 28 Sept 2026.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
+          <t>VAT rate</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="inlineStr">
+        <is>
+          <t>Current South African VAT rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Managed Service Retainer</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>R1,500/month excl. VAT</t>
+        </is>
+      </c>
+      <c r="C9" s="32" t="inlineStr">
+        <is>
+          <t>Set by Gerhard (26 Sept 2026) - a lighter monthly retainer to keep the recurring bill low relative to Herotel and support the case for the build investment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
           <t>Contract term - Vodacom Business Connect</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>36 months</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>Confirmed 28 Sept 2026 against the CTTX Vodacom Reseller price book (Duane Forlee, Vodacom, 29 May 2026): the 36-month rate is slightly lower than 24-month. Monthly figure in this model is the confirmed 36-month client price at CTTX's standard 20% markup.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Design Assumptions</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="31" t="inlineStr">
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>Single 9m mast carrying two 90-degree sector antennas (confirmed by Gerhard, 26 Sept 2026) - replaces the lodge's existing leaning gum-pole mount. This is NOT a two-site build; earlier drafts of this costing incorrectly read the field survey's two radio labels as two separate physical locations before this was corrected.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="31" t="inlineStr">
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>Line-of-sight confirmed for all 28 subscriber links by Abel Ringisai's field RF survey (KML export, 22 Sept 2026).</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="31" t="inlineStr">
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>The longest links (1.7km-3.0km, to the staff village and Director's House) sit at the edge of the serving sector's range and still need a link-budget check to confirm they sustain full 100 Mbps symmetrical - flagged, not yet resolved.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="32" t="inlineStr">
         <is>
           <t>Cable run priced at an average 40m per run - to be confirmed once exact distances are measured on site.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="31" t="inlineStr">
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>Vodacom Business Connect feasibility for this specific site has not yet been formally submitted/approved.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>What's Included in the 10-Year Support</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="31" t="inlineStr">
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="32" t="inlineStr">
         <is>
           <t>Years 1-3: monthly remote monitoring, quarterly on-site maintenance, 24/7 emergency support, proactive performance reporting, warranty-covered equipment troubleshooting/replacement.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="31" t="inlineStr">
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="32" t="inlineStr">
         <is>
           <t>Years 4-10: ongoing remote monitoring, annual on-site maintenance/assessment, 24/7 support continuation, planned technology refresh, performance reporting.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="31" t="inlineStr">
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="32" t="inlineStr">
         <is>
           <t>Throughout: no vendor lock-in on the owned hardware, scalability support, staff training and documentation.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>What's Excluded / Not Yet Priced</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="31" t="inlineStr">
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t>Major component replacement (Lithium battery bank, inverter) near the end of the 10-year term - typical service life for this equipment is 8-10 years, so a replacement reserve may be needed in years 8-10 and is not included in the build cost above.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="31" t="inlineStr">
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="32" t="inlineStr">
         <is>
           <t>Trenching or underground civil works (none required - this is a wireless solution).</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="31" t="inlineStr">
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="32" t="inlineStr">
         <is>
           <t>CCTV cameras, POS hardware, or other endpoint devices not listed in the hardware BOM.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="31" t="inlineStr">
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="32" t="inlineStr">
         <is>
           <t>Travel/accommodation beyond a day-trip assumption from Port Elizabeth (~1h45 drive) - to be confirmed if overnight stays are required during the 3-day install.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="31" t="inlineStr">
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="32" t="inlineStr">
         <is>
           <t>Any scope beyond the confirmed coverage zones (28 subscriber sites) without a signed change order.</t>
         </is>
@@ -2728,23 +2818,23 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A10:C10"/>
     <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A28:C28"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A18:C18"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A29:C29"/>
     <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/proposals/Barefoot_5Year_Business_Case.xlsx
+++ b/proposals/Barefoot_5Year_Business_Case.xlsx
@@ -2563,7 +2563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2639,178 +2639,229 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Timing of the comparison</t>
+          <t>Payment terms - build</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>Both paths start at month 1</t>
+          <t>50% deposit on order, 50% on commissioning</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
         <is>
-          <t>Year 0 is the build payment only. Neither path is charged any monthly bill in year 0 - an earlier version of this model charged Herotel a full year before the build and gave the CTTX path none, which overstated the case. Corrected 28 Sept 2026.</t>
+          <t>The deposit places the equipment order and secures the allocation. Both halves fall in year 0 of the cash flow, so the model is unchanged by the split.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>VAT rate</t>
+          <t>Accounting treatment - build</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>Capital expenditure (fixed asset)</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
         <is>
-          <t>Current South African VAT rate.</t>
+          <t>R308,696 ex VAT is capitalised as owned infrastructure on the lodge's balance sheet; the R46,304 input VAT is recoverable for a VAT-registered entity; the asset is depreciable over its working life and transfers with the property. The lodge's accountant confirms the exact treatment - this workbook does not model the tax effect (which would only improve the case).</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Managed Service Retainer</t>
+          <t>Spa and future endpoints</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>R1,500/month excl. VAT</t>
+          <t>Not in the current-provider line</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
         <is>
-          <t>Set by Gerhard (26 Sept 2026) - a lighter monthly retainer to keep the recurring bill low relative to Herotel and support the case for the build investment.</t>
+          <t>The current bill excludes the spa (not connected today). On the rental model each additional AP is ~R263/month incl. VAT (per the current invoice) plus a link to reach the spa; on the owned network it is a once-off hardware cost. Left out of the comparison deliberately - the current-provider line is therefore understated, not overstated.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
+          <t>Timing of the comparison</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Both paths start at month 1</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="inlineStr">
+        <is>
+          <t>Year 0 is the build payment only. Neither path is charged any monthly bill in year 0 - an earlier version of this model charged Herotel a full year before the build and gave the CTTX path none, which overstated the case. Corrected 28 Sept 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>VAT rate</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="inlineStr">
+        <is>
+          <t>Current South African VAT rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Managed Service Retainer</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>R1,500/month excl. VAT</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>Set by Gerhard (26 Sept 2026) - a lighter monthly retainer to keep the recurring bill low relative to Herotel and support the case for the build investment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
           <t>Contract term - Vodacom Business Connect</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>36 months</t>
         </is>
       </c>
-      <c r="C10" s="32" t="inlineStr">
+      <c r="C13" s="32" t="inlineStr">
         <is>
           <t>Confirmed 28 Sept 2026 against the CTTX Vodacom Reseller price book (Duane Forlee, Vodacom, 29 May 2026): the 36-month rate is slightly lower than 24-month. Monthly figure in this model is the confirmed 36-month client price at CTTX's standard 20% markup.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Design Assumptions</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="32" t="inlineStr">
-        <is>
-          <t>Single 9m mast carrying two 90-degree sector antennas (confirmed by Gerhard, 26 Sept 2026) - replaces the lodge's existing leaning gum-pole mount. This is NOT a two-site build; earlier drafts of this costing incorrectly read the field survey's two radio labels as two separate physical locations before this was corrected.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="32" t="inlineStr">
-        <is>
-          <t>Line-of-sight confirmed for all 28 subscriber links by Abel Ringisai's field RF survey (KML export, 22 Sept 2026).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="32" t="inlineStr">
-        <is>
-          <t>The longest links (1.7km-3.0km, to the staff village and Director's House) sit at the edge of the serving sector's range and still need a link-budget check to confirm they sustain full 100 Mbps symmetrical - flagged, not yet resolved.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="32" t="inlineStr">
         <is>
-          <t>Cable run priced at an average 40m per run - to be confirmed once exact distances are measured on site.</t>
+          <t>Single 9m mast carrying two 90-degree sector antennas (confirmed by Gerhard, 26 Sept 2026) - replaces the lodge's existing leaning gum-pole mount. This is NOT a two-site build; earlier drafts of this costing incorrectly read the field survey's two radio labels as two separate physical locations before this was corrected.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="32" t="inlineStr">
         <is>
-          <t>Vodacom Business Connect feasibility for this specific site has not yet been formally submitted/approved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>What's Included in the 10-Year Support</t>
+          <t>Line-of-sight confirmed for all 28 subscriber links by Abel Ringisai's field RF survey (KML export, 22 Sept 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>The longest links (1.7km-3.0km, to the staff village and Director's House) sit at the edge of the serving sector's range and still need a link-budget check to confirm they sustain full 100 Mbps symmetrical - flagged, not yet resolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t>Cable run priced at an average 40m per run - to be confirmed once exact distances are measured on site.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="32" t="inlineStr">
         <is>
+          <t>Vodacom Business Connect feasibility for this specific site has not yet been formally submitted/approved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>What's Included in the 10-Year Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="32" t="inlineStr">
+        <is>
           <t>Years 1-3: monthly remote monitoring, quarterly on-site maintenance, 24/7 emergency support, proactive performance reporting, warranty-covered equipment troubleshooting/replacement.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="32" t="inlineStr">
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="32" t="inlineStr">
         <is>
           <t>Years 4-10: ongoing remote monitoring, annual on-site maintenance/assessment, 24/7 support continuation, planned technology refresh, performance reporting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="32" t="inlineStr">
-        <is>
-          <t>Throughout: no vendor lock-in on the owned hardware, scalability support, staff training and documentation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>What's Excluded / Not Yet Priced</t>
         </is>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="32" t="inlineStr">
         <is>
-          <t>Major component replacement (Lithium battery bank, inverter) near the end of the 10-year term - typical service life for this equipment is 8-10 years, so a replacement reserve may be needed in years 8-10 and is not included in the build cost above.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="32" t="inlineStr">
-        <is>
-          <t>Trenching or underground civil works (none required - this is a wireless solution).</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="32" t="inlineStr">
-        <is>
-          <t>CCTV cameras, POS hardware, or other endpoint devices not listed in the hardware BOM.</t>
+          <t>Throughout: no vendor lock-in on the owned hardware, scalability support, staff training and documentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>What's Excluded / Not Yet Priced</t>
         </is>
       </c>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="32" t="inlineStr">
         <is>
-          <t>Travel/accommodation beyond a day-trip assumption from Port Elizabeth (~1h45 drive) - to be confirmed if overnight stays are required during the 3-day install.</t>
+          <t>Major component replacement (Lithium battery bank, inverter) near the end of the 10-year term - typical service life for this equipment is 8-10 years, so a replacement reserve may be needed in years 8-10 and is not included in the build cost above.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="32" t="inlineStr">
+        <is>
+          <t>Trenching or underground civil works (none required - this is a wireless solution).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="32" t="inlineStr">
+        <is>
+          <t>CCTV cameras, POS hardware, or other endpoint devices not listed in the hardware BOM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="32" t="inlineStr">
+        <is>
+          <t>Travel/accommodation beyond a day-trip assumption from Port Elizabeth (~1h45 drive) - to be confirmed if overnight stays are required during the 3-day install.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="32" t="inlineStr">
         <is>
           <t>Any scope beyond the confirmed coverage zones (28 subscriber sites) without a signed change order.</t>
         </is>
@@ -2820,22 +2871,22 @@
   <mergeCells count="18">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A13:C13"/>
     <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A31:C31"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A18:C18"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
